--- a/daily_matches/job_matches_2026-03-12.xlsx
+++ b/daily_matches/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Machine Learning Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beusa Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1afb886e29207d11</t>
+          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>AWS Engineer - Remote - Contract</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ThoughtSpot</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, Snowflake, BigQuery, Redshift, Tableau, MicroStrategy, Python</t>
+          <t>RAG, Gemini, EC2, Redshift, Docker, CI/CD, Jenkins, Terraform, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e36f4fe75596b0</t>
+          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI - Spread Products</t>
+          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, MLflow, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b062d6862ec7b49f</t>
+          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Krispy Kreme</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, XGBoost, CI/CD, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, EC2, Kinesis, FastAPI, CI/CD, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720ef9242159fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, TikTok AIGC Agentic Workflow</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>National Kidney Foundation of Michigan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Kubernetes, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92683535bc9c1a79</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, TikTok AIGC Agentic Workflow</t>
+          <t>Data Scientist, Lightroom</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Kubernetes, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,77 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686efb497325c563</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sr. Business Data Analyst</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Live Nation</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Beverly Hills, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Data Lake, Snowflake, Databricks, PySpark, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb1a84c567a33bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Roblox DB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e42015eacfe1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=dceb47382775f627</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-12.xlsx
+++ b/daily_matches/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba67a631e791b80</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdbba492c2f4bb4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Engineer - Remote - Contract</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navat Technologies Pvt Ltd</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, EC2, Redshift, Docker, CI/CD, Jenkins, Terraform, Redshift, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ff1920a00572de</t>
+          <t>https://www.indeed.com/viewjob?jk=1215d222f0829a74</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Vehicle Chassis Systems</t>
+          <t>Managing Data Architect - Azure Databricks Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,122 +556,682 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, MLflow, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Gemini, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edec9672be03e5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1be5d66c0b6da3c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Computer Vision Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Matrix Design Group, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Newburgh, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, EC2, Kinesis, FastAPI, CI/CD, Git, MySQL, Python, SQL</t>
+          <t>RAG, LLaMA, Pinecone, TensorFlow, PyTorch, YOLO, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dce5307329a37fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4369dc198ca6c7d2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Kidney Foundation of Michigan</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Snowflake, Databricks, Python, R</t>
+          <t>Data Scientist, RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c9a61c1f4f4962</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4a0fc38ba3e2b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist, Lightroom</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f701cd607ccab481</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Inframark</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc5eefd4bc93ea8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Generative AI (GenAI) Developer / Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7a9a45148c6cfc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Berwyn, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=630e60f9fece90b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Production Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Placer.ai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5481df28409f336</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Glue, Data Lake, Kubernetes, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c815831b07a9f2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer, Striper Experience</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Foot Locker</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b34515a4df838c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Application Platform Architect - 6163848</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Hadoop, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17f23620eb37b83f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>come and see</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=433680cdbabbcc69</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HireMaven</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=469ca114eda259a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Databricks Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc2eab297cb5f7ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=346934ccf1363e50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Agentic DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ffdf90ff0031002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HERE Technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Glue, Athena, Redshift, Redshift, Tableau, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6422368c0b16532</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Industry &amp; Function AI Decision Science Consultant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb84b99e8ae43beb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c8c594c89955854</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Labor Management</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lakeland, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dceb47382775f627</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9834656ac2bda8ee</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-12.xlsx
+++ b/daily_matches/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Generative AI Intelligence Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trailhead Biosystems Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Pinecone, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046e9fc9862574e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b12508cb4f85945</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer (Value Engineering) - Public Sector</t>
+          <t>Gen AI Engineer-7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2031b8bc315c3e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4865e4c90a2c26ed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Gen AI Engineer-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,1337 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ea55d42813786d</t>
+          <t>https://www.indeed.com/viewjob?jk=7697ef35e7f57296</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer IV - Operations</t>
+          <t>Gen AI Engineer (Remote)-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Autonomous Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdc6601b15f0efb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d377e0ee0cb3113a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Compliance Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Dataflow, CI/CD, Jenkins, Terraform, Git, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbbb3064921ed9dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chubb Insurance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=197cff4aafdfaea9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chubb Insurance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57fd573a0e10c0a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Architect-1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c3456172cfa865b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Architect-1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2f8f0a19bc72bb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Architect-1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=110211630f4fc02c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Generative AI Developer-6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f36cc095b2fcbcef</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Generative AI Developer-6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4924fb1b781ca84</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Generative AI Developer-6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1b145c1e2f8f8d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Cloud IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=222b7e1a2c648adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IAM Automation &amp; Workflow Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, PyTorch, OpenCV, EC2, Docker, Kubernetes, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=900a1527df2d6e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AWS Developer / Administrator</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e375c96c31b3003e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GenAI Engineer-4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbccfda85c6a1d5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>REN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Dataflow, Terraform, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bde7942b264b382</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data scientist-6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178806c56968db85</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. AI Platform Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Confianza Technologies LLC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Hugging Face, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fd3ec6f6ef6040</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60b94a69d091956b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Achieve Debt Relief</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7fb320ef12c27c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Achieve Debt Relief</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=799867eea8021b82</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Achieve Debt Relief</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=020f32069d33c332</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Achieve Debt Relief</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1bff485c203bf9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Finance of America</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Python, R, Julia, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5f9198e5c83f6a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Achieve Debt Relief</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f85913f00ef683c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr Cloud Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b29f5bdd364c3785</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Python Engineer-6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d163fd779e48c6f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Big Data and Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Git, MongoDB, NoSQL, Tableau, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7a3dca159b15bd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sutter Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Azure ML, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09c5944318c882ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=892575ef34626b3a</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eebf1fc1c67b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Generative AI Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a70267facdcee64</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IAM Automation &amp; Workflow Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Prompt Engineering, S3, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1abe9b96fc924d67</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer- MS Fabric</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>APR Supply Co.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lebanon, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Dataflow, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=560029269acb4918</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cloud Azure Tools Specialist</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Arbitration Forums Inc.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, TensorFlow, PyTorch, Azure ML, Snowflake, Databricks, Power BI, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37c7e4f119145c27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer-7</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f139205c340a82a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GEN AI Engineer-6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9047f1615639c126</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GEN AI Engineer-6</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4285819f89694c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer, Security</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CentralReach</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Holmdel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4178bba7281e09e9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-12.xlsx
+++ b/daily_matches/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer, Design Innovation</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, S3, Docker, CI/CD, Jenkins</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93163132c02c54e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot - Full Stack</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>JET Infrastructure Holding IA LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, RAG, Copilot, Synapse, Dataflow, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e50f142a88c764d</t>
+          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Scientist (Automotive Safety)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, spaCy, BigQuery, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d104ab38a81dc87</t>
+          <t>https://www.indeed.com/viewjob?jk=6922ce3d1536f05f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Technical Data Analyst</t>
+          <t>AI/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GHX</t>
+          <t>Mission Produce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Git, Snowflake, Redshift, Polars, Tableau, Power BI, Python, SQL</t>
+          <t>Machine Learning Engineer, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Synapse, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b94c4bc25bde3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0af3bdc55914e6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Senior Full Stack Software Engineer - DNEE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Schrödinger</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d57c13f84c6ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab628f31681189</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Norm AI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, YOLO, Glue, Redshift, Snowflake, Redshift, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0ec20af150bf35</t>
+          <t>https://www.indeed.com/viewjob?jk=fc988507a8fbe5a4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>BI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, Jenkins, Hadoop, NoSQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9762eaa0bc5ffa44</t>
+          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2648a943e79df3d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Otsuka</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Synapse, Dataflow, Kubernetes, Terraform, Git, Databricks, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a979955044514</t>
+          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Salesforce Engineer</t>
+          <t>Cloud FinOps &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rancho Belago, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, CI/CD, Terraform, Tableau, Power BI, Quicksight, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,637 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509c48f4bc1ead70</t>
+          <t>https://www.indeed.com/viewjob?jk=23cc05b43d7df127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Salesforce Engineer</t>
+          <t>Senior Artificial Intelligence Software Engineer (Hybrid Eligible)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Oak Ridge National Laboratory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef4b2c672ff10829</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hayden AI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6ca54fa35f4880f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist - Supply Chain Optimization</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Docker, CI/CD, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eacd62fcdaf0914</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lowell, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed94196ad8588dc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Financial Data</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CLAIR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, XGBoost, MLflow, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcd9bde5e7abff2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior DevOps Software Engineer (AI)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brahma Consulting Group</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5045eb4f1ca1c9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Credit Underwriting</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLAIR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9041f7342962c394</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, CI/CD, Git, Snowflake, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fd3ab5f70384de6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer (Enterprise Data &amp; Apps)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Wasserman Media Group LLC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=810ecea9aa0b6d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>REFRAME Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c946ae164f40d4eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, GTM Strategy &amp; Transformation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Kubernetes, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e0b5650d3d4b95</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a348b32118783e</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14e279ac54f0b0af</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=202b0e0bdfb4c796</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PyTorch, S3, Docker, CI/CD, Snowflake, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Analyst/Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df9574a0fde318ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Claims Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist, Analytics- Hybrid</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vivint</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Databricks, BigQuery, Tableau, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30627f68c0b20d5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist, Analytics- Hybrid</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vivint</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Databricks, BigQuery, Tableau, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6773099888037e47</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-12.xlsx
+++ b/daily_matches/job_matches_2026-03-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Software Engineer Sr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
+          <t>Data Scientist, RAG, AWS SageMaker, S3, Glue, Athena, Redshift, Synapse, Data Lake, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ecb9f752d7e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2de7e18b2b69e7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Engineer - AWS Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JET Infrastructure Holding IA LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Synapse, Dataflow, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Generative AI, RAG, Gemini, S3, Glue, Athena, Redshift, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec57a01407f829f</t>
+          <t>https://www.indeed.com/viewjob?jk=ada71137ca1084e0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist (Automotive Safety)</t>
+          <t>Data Scientist-Generative AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, spaCy, BigQuery, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6922ce3d1536f05f</t>
+          <t>https://www.indeed.com/viewjob?jk=59c593bcc2ffb999</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Test Engineer - AI/LLM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Synapse, CI/CD, GitHub Actions, Terraform</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0af3bdc55914e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5ad635b4410c94</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - DNEE</t>
+          <t>Data Engineer, Field Reliability</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, Cassandra, NoSQL, SQL</t>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, PySpark, Kafka, Tableau, Matplotlib</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab628f31681189</t>
+          <t>https://www.indeed.com/viewjob?jk=910d18590f9df945</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Solutions Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Norm AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc988507a8fbe5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=208a2b8008157acb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BI Data Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Jenkins, Hadoop, NoSQL, Tableau, Python, SQL</t>
+          <t>RAG, TensorFlow, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2543168971c5287</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea8e333bf7a2127</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb44cfe22f2062c3</t>
+          <t>https://www.indeed.com/viewjob?jk=36e23f2661209cd3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer IV, Field Sales Reporting, Commercial IT</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Otsuka</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, Kubernetes, Terraform, Git, Databricks, Power BI, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, BigQuery, CI/CD, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa82edf7b00984b3</t>
+          <t>https://www.indeed.com/viewjob?jk=331501b10e21bc6f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud FinOps &amp; DevOps Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Terraform, Tableau, Power BI, Quicksight, Python, SQL, R</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cc05b43d7df127</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ae1ac54f4758f5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Software Engineer (Hybrid Eligible)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Python</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4b2c672ff10829</t>
+          <t>https://www.indeed.com/viewjob?jk=882043ad70945702</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hayden AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ca54fa35f4880f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d3cb1179f1dc88c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist - Supply Chain Optimization</t>
+          <t>Specialist, Data Engineer - NF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Docker, CI/CD, Git, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eacd62fcdaf0914</t>
+          <t>https://www.indeed.com/viewjob?jk=7921cb7720ce5e14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Senior Engineer, Enterprise AI Services</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed94196ad8588dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=505c2da8b1732d98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Financial Data</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, XGBoost, MLflow, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Kinesis, Jenkins, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd9bde5e7abff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=007797d3a89d473c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer (AI)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brahma Consulting Group</t>
+          <t>SHEIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5045eb4f1ca1c9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=2d19b3915e6dfbce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Credit Underwriting</t>
+          <t>Sr. Data Scientist - Gen AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, AWS SageMaker, Azure ML, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9041f7342962c394</t>
+          <t>https://www.indeed.com/viewjob?jk=25eaecceae7cfa0a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CereHive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Git, Snowflake, Hadoop, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd3ab5f70384de6</t>
+          <t>https://www.indeed.com/viewjob?jk=f97ddc36649b8489</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Enterprise Data &amp; Apps)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wasserman Media Group LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Databricks, Kafka, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=810ecea9aa0b6d35</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f3c2041c813633</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REFRAME Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Databricks, Kafka, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c946ae164f40d4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35fd804f9b76dd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, GTM Strategy &amp; Transformation</t>
+          <t>GenAI / Agentic AI / ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Kubernetes, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, AWS SageMaker, Azure ML, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e0b5650d3d4b95</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16b43d0f30d8a5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist III</t>
+          <t>Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Databricks, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e279ac54f0b0af</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd63ec5f3e76f37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer II</t>
+          <t>Sr.Dot Net Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202b0e0bdfb4c796</t>
+          <t>https://www.indeed.com/viewjob?jk=dcefdde010d03c39</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Agentic AI Solution Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>coras</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PyTorch, S3, Docker, CI/CD, Snowflake, PySpark, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb29970206c5f72d</t>
+          <t>https://www.indeed.com/viewjob?jk=f79d8d36c5e55836</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Analyst/Engineer</t>
+          <t>Sr. Software Engineer, Personal Loans Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9574a0fde318ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa94251afe4fef8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Data Scientist — Clinical Analytics &amp; Automation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Clearview Cancer Institute</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Apache Airflow, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e5fd8d4039af6</t>
+          <t>https://www.indeed.com/viewjob?jk=19f4b42d41b58c0e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Scientist, Analytics- Hybrid</t>
+          <t>Data &amp; Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>workbay</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,52 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Databricks, BigQuery, Tableau, Python, SQL, R, Hypothesis Testing</t>
+          <t>Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30627f68c0b20d5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist, Analytics- Hybrid</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Vivint</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, BigQuery, Databricks, BigQuery, Tableau, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6773099888037e47</t>
+          <t>https://www.indeed.com/viewjob?jk=9b02a9cd3ab5c56d</t>
         </is>
       </c>
     </row>
